--- a/exports/TATAPOWER_full_report.xlsx
+++ b/exports/TATAPOWER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.94</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>242.7</v>
+        <v>232.5</v>
       </c>
       <c r="I2" t="n">
         <v>235.4301010417526</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>4.43</v>
+        <v>0.04</v>
       </c>
       <c r="L2" t="n">
-        <v>0.86</v>
+        <v>1.18</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>6.08</v>
       </c>
       <c r="O2" t="n">
         <v>0.92</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>249.8</v>
+        <v>250.95</v>
       </c>
       <c r="I3" t="n">
         <v>249.8503707502739</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.44</v>
+        <v>-7.94</v>
       </c>
       <c r="L3" t="n">
         <v>10.26</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.56</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44599.55208333334</v>
+        <v>44600.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>251.5</v>
+        <v>235.45</v>
       </c>
       <c r="I4" t="n">
         <v>237.8763648858179</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0.22</v>
+        <v>-6.18</v>
       </c>
       <c r="L4" t="n">
-        <v>0.68</v>
+        <v>7.27</v>
       </c>
       <c r="M4" t="n">
         <v>0.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.12</v>
+        <v>7.24</v>
       </c>
       <c r="O4" t="n">
         <v>0.28</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.3</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>223</v>
+        <v>225.9</v>
       </c>
       <c r="I5" t="n">
         <v>225.2014039952437</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>5.29</v>
+        <v>4.06</v>
       </c>
       <c r="L5" t="n">
         <v>7.71</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.54</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>273</v>
+        <v>257.7</v>
       </c>
       <c r="I6" t="n">
         <v>268.1659392657555</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K6" t="n">
-        <v>20.85</v>
+        <v>14.08</v>
       </c>
       <c r="L6" t="n">
         <v>5.98</v>
@@ -783,7 +854,7 @@
         <v>2.03</v>
       </c>
       <c r="N6" t="n">
-        <v>3.62</v>
+        <v>5.51</v>
       </c>
       <c r="O6" t="n">
         <v>1.19</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.08</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44746.38541666666</v>
+        <v>44746.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>208.95</v>
+        <v>212.75</v>
       </c>
       <c r="I7" t="n">
         <v>212.5272553669172</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>77</v>
+        <v>77.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>18.92</v>
+        <v>17.44</v>
       </c>
       <c r="L7" t="n">
         <v>3.96</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.21</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44768.55208333334</v>
+        <v>44769.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>225.5</v>
+        <v>217.65</v>
       </c>
       <c r="I8" t="n">
         <v>223.6963613790409</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>5.99</v>
+        <v>2.3</v>
       </c>
       <c r="L8" t="n">
         <v>2.09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.46</v>
+        <v>2.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>2.68</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44774.38541666666</v>
+        <v>44774.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>228.05</v>
+        <v>230.8</v>
       </c>
       <c r="I9" t="n">
         <v>228.4782922992113</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.78</v>
+        <v>-6.04</v>
       </c>
       <c r="L9" t="n">
-        <v>5.21</v>
+        <v>6.23</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.79</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>232</v>
+        <v>227.6</v>
       </c>
       <c r="I10" t="n">
         <v>228.2695739805186</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.52</v>
+        <v>-1.39</v>
       </c>
       <c r="L10" t="n">
         <v>2.32</v>
@@ -1011,7 +1130,7 @@
         <v>0.35</v>
       </c>
       <c r="N10" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="O10" t="n">
         <v>3.96</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.63</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44809.55208333334</v>
+        <v>44810.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>236.75</v>
+        <v>245.55</v>
       </c>
       <c r="I11" t="n">
         <v>238.7837852957973</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.02</v>
+        <v>-7.89</v>
       </c>
       <c r="L11" t="n">
-        <v>5.56</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>0.63</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4.54</v>
       </c>
       <c r="O11" t="n">
         <v>-3.06</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.76</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>236.4</v>
+        <v>233.3</v>
       </c>
       <c r="I12" t="n">
         <v>235.274807482593</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.73</v>
+        <v>-4.99</v>
       </c>
       <c r="L12" t="n">
         <v>5.23</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.29</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44861.38541666666</v>
+        <v>44861.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>224.4</v>
+        <v>226.8</v>
       </c>
       <c r="I13" t="n">
         <v>225.9607988165847</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>3.81</v>
+        <v>2.79</v>
       </c>
       <c r="L13" t="n">
         <v>1.99</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.97</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44882.38541666666</v>
+        <v>44882.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>222.85</v>
+        <v>221.4</v>
       </c>
       <c r="I14" t="n">
         <v>222.8391836432502</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.74</v>
+        <v>-2.38</v>
       </c>
       <c r="L14" t="n">
         <v>2.56</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>4.28</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44900.55208333334</v>
+        <v>44901.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>225</v>
+        <v>228.35</v>
       </c>
       <c r="I15" t="n">
         <v>227.4539803118013</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.63</v>
+        <v>-3.14</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>4.02</v>
       </c>
       <c r="M15" t="n">
         <v>0.43</v>
       </c>
       <c r="N15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
         <v>-1.56</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.06</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44904.38541666666</v>
+        <v>44904.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>220.8</v>
+        <v>219.75</v>
       </c>
       <c r="I16" t="n">
         <v>220.7151460765423</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.31</v>
+        <v>-3.77</v>
       </c>
       <c r="L16" t="n">
-        <v>3.77</v>
+        <v>4.75</v>
       </c>
       <c r="M16" t="n">
         <v>0.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>3.74</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>210.8</v>
+        <v>212</v>
       </c>
       <c r="I17" t="n">
         <v>211.0050392900561</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K17" t="n">
-        <v>4.07</v>
+        <v>3.53</v>
       </c>
       <c r="L17" t="n">
         <v>2.3</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>5.04</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>202.45</v>
+        <v>200.1</v>
       </c>
       <c r="I18" t="n">
         <v>201.9503689009925</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.5</v>
+        <v>-5.61</v>
       </c>
       <c r="L18" t="n">
-        <v>5.24</v>
+        <v>7.19</v>
       </c>
       <c r="M18" t="n">
         <v>0.24</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>3.91</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>205.1</v>
+        <v>212.4</v>
       </c>
       <c r="I19" t="n">
         <v>207.9262261676529</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.5</v>
+        <v>-6.15</v>
       </c>
       <c r="L19" t="n">
-        <v>2.85</v>
+        <v>7.62</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02</v>
+        <v>4.78</v>
       </c>
       <c r="N19" t="n">
         <v>0.6899999999999999</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.63</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44979.55208333334</v>
+        <v>44980.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>202.6</v>
+        <v>202.25</v>
       </c>
       <c r="I20" t="n">
         <v>202.5578880114029</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.61</v>
+        <v>-4.78</v>
       </c>
       <c r="L20" t="n">
         <v>7.16</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.1</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>205.45</v>
+        <v>207.65</v>
       </c>
       <c r="I21" t="n">
         <v>206.8460746303209</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.58</v>
+        <v>-2.67</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3.46</v>
       </c>
       <c r="M21" t="n">
         <v>0.5</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>3.6</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>206.35</v>
+        <v>203.4</v>
       </c>
       <c r="I22" t="n">
         <v>204.3708499609951</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.63</v>
+        <v>-2.05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.79</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.58</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45021.38541666666</v>
+        <v>45021.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>193.5</v>
+        <v>194.55</v>
       </c>
       <c r="I23" t="n">
         <v>194.3921984822456</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K23" t="n">
-        <v>4.87</v>
+        <v>4.35</v>
       </c>
       <c r="L23" t="n">
         <v>1.62</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.02</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45064.38541666666</v>
+        <v>45064.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>206.65</v>
+        <v>204.7</v>
       </c>
       <c r="I24" t="n">
         <v>204.9910758711751</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42.83333333333334</v>
+        <v>43</v>
       </c>
       <c r="K24" t="n">
-        <v>6.22</v>
+        <v>5.22</v>
       </c>
       <c r="L24" t="n">
         <v>1.26</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.55</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I25" t="n">
         <v>212.9333961088298</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.57</v>
+        <v>-4.05</v>
       </c>
       <c r="L25" t="n">
         <v>4.45</v>
@@ -1866,7 +2165,7 @@
         <v>0.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.03</v>
+        <v>2.69</v>
       </c>
       <c r="O25" t="n">
         <v>-1.59</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.33</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>219</v>
+        <v>217.75</v>
       </c>
       <c r="I26" t="n">
         <v>217.8127058440659</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>2.82</v>
+        <v>2.23</v>
       </c>
       <c r="L26" t="n">
         <v>0.61</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>4.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45112.55208333334</v>
+        <v>45113.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>221.8</v>
+        <v>227.75</v>
       </c>
       <c r="I27" t="n">
         <v>225.6962437403794</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.86</v>
+        <v>-4.59</v>
       </c>
       <c r="L27" t="n">
-        <v>2.96</v>
+        <v>5.07</v>
       </c>
       <c r="M27" t="n">
-        <v>0.53</v>
+        <v>1.44</v>
       </c>
       <c r="N27" t="n">
-        <v>1.53</v>
+        <v>3.63</v>
       </c>
       <c r="O27" t="n">
         <v>-1.47</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.21</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45120.55208333334</v>
+        <v>45121.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>222.25</v>
+        <v>219.65</v>
       </c>
       <c r="I28" t="n">
         <v>220.4827812177651</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.41</v>
+        <v>-3.56</v>
       </c>
       <c r="L28" t="n">
-        <v>3.01</v>
+        <v>4.04</v>
       </c>
       <c r="M28" t="n">
         <v>0.07000000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>4.33</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>221.1</v>
+        <v>232.65</v>
       </c>
       <c r="I29" t="n">
         <v>224.4603726674476</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.66</v>
+        <v>-5.92</v>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>7.99</v>
       </c>
       <c r="M29" t="n">
         <v>0.46</v>
       </c>
       <c r="N29" t="n">
-        <v>1.15</v>
+        <v>6.33</v>
       </c>
       <c r="O29" t="n">
         <v>-0.47</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.39</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>235.7</v>
+        <v>230.65</v>
       </c>
       <c r="I30" t="n">
         <v>231.7610969885318</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K30" t="n">
-        <v>1.31</v>
+        <v>-0.86</v>
       </c>
       <c r="L30" t="n">
         <v>5.44</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.92</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45160.38541666666</v>
+        <v>45160.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>240.8</v>
+        <v>243.7</v>
       </c>
       <c r="I31" t="n">
         <v>241.0567409535557</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.4</v>
+        <v>-5.66</v>
       </c>
       <c r="L31" t="n">
-        <v>5.18</v>
+        <v>5.83</v>
       </c>
       <c r="M31" t="n">
         <v>0.83</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.3</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>261.75</v>
+        <v>257.1</v>
       </c>
       <c r="I32" t="n">
         <v>257.3410572127118</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>7.41</v>
+        <v>5.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.35</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>5.88</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>244.45</v>
+        <v>250.9</v>
       </c>
       <c r="I33" t="n">
         <v>246.6149958862498</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K33" t="n">
-        <v>4.92</v>
+        <v>2.41</v>
       </c>
       <c r="L33" t="n">
         <v>3.66</v>
       </c>
       <c r="M33" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="N33" t="n">
         <v>3.33</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.34</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>338.05</v>
+        <v>320.1</v>
       </c>
       <c r="I34" t="n">
         <v>321.1113803944845</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>34.73</v>
+        <v>27.58</v>
       </c>
       <c r="L34" t="n">
         <v>2.11</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.18</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45301.38541666666</v>
+        <v>45301.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>343.45</v>
+        <v>346.8</v>
       </c>
       <c r="I35" t="n">
         <v>344.9360339950288</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.29</v>
+        <v>-8.34</v>
       </c>
       <c r="L35" t="n">
         <v>9.25</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.39</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>391</v>
+        <v>367.9</v>
       </c>
       <c r="I36" t="n">
         <v>382.4109059832455</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>12.75</v>
+        <v>6.08</v>
       </c>
       <c r="L36" t="n">
         <v>3.32</v>
       </c>
       <c r="M36" t="n">
-        <v>0.58</v>
+        <v>2.84</v>
       </c>
       <c r="N36" t="n">
-        <v>4.61</v>
+        <v>7.44</v>
       </c>
       <c r="O36" t="n">
         <v>1.73</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>11.2</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>375.85</v>
+        <v>391.85</v>
       </c>
       <c r="I37" t="n">
         <v>385.3390487890053</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.16</v>
+        <v>-6.51</v>
       </c>
       <c r="L37" t="n">
-        <v>4.96</v>
+        <v>7.09</v>
       </c>
       <c r="M37" t="n">
         <v>1.89</v>
       </c>
       <c r="N37" t="n">
-        <v>2.43</v>
+        <v>4.4</v>
       </c>
       <c r="O37" t="n">
         <v>-7.44</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.95</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45363.38541666666</v>
+        <v>45363.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>400.15</v>
+        <v>396.4</v>
       </c>
       <c r="I38" t="n">
         <v>397.4021606327343</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>2.12</v>
+        <v>1.16</v>
       </c>
       <c r="L38" t="n">
         <v>2.97</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45385.38541666666</v>
+        <v>45385.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>410.8</v>
+        <v>412.6</v>
       </c>
       <c r="I39" t="n">
         <v>411.595081001179</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.63</v>
+        <v>-4.09</v>
       </c>
       <c r="L39" t="n">
         <v>4.76</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.03</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>446.9</v>
+        <v>433.7</v>
       </c>
       <c r="I40" t="n">
         <v>438.7294504508156</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K40" t="n">
-        <v>8.31</v>
+        <v>5.11</v>
       </c>
       <c r="L40" t="n">
         <v>1.1</v>
@@ -2721,7 +3200,7 @@
         <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>1.03</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.55</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45429.55208333334</v>
+        <v>45430.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>435.5</v>
+        <v>441.05</v>
       </c>
       <c r="I41" t="n">
         <v>436.3923567571247</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.42</v>
+        <v>-1.69</v>
       </c>
       <c r="L41" t="n">
         <v>3.59</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>5.8</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45442.38541666666</v>
+        <v>45442.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>430.65</v>
+        <v>427.35</v>
       </c>
       <c r="I42" t="n">
         <v>428.7306938882213</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.36</v>
+        <v>-3.11</v>
       </c>
       <c r="L42" t="n">
-        <v>2.94</v>
+        <v>4.19</v>
       </c>
       <c r="M42" t="n">
         <v>0.57</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>4.68</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>437.8</v>
+        <v>456.65</v>
       </c>
       <c r="I43" t="n">
         <v>447.3427521080733</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.45</v>
+        <v>-6.86</v>
       </c>
       <c r="L43" t="n">
-        <v>2.66</v>
+        <v>7.64</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>4.35</v>
       </c>
       <c r="O43" t="n">
         <v>-1.42</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.44</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>456.85</v>
+        <v>408.25</v>
       </c>
       <c r="I44" t="n">
         <v>432.1433878418931</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.04</v>
+        <v>-10.6</v>
       </c>
       <c r="L44" t="n">
-        <v>2.04</v>
+        <v>18.61</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>11.24</v>
       </c>
       <c r="O44" t="n">
         <v>4.35</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>13.6</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>424.75</v>
+        <v>441.65</v>
       </c>
       <c r="I45" t="n">
         <v>437.9757938266284</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.04</v>
+        <v>-8.18</v>
       </c>
       <c r="L45" t="n">
         <v>12.41</v>
@@ -3006,7 +3545,7 @@
         <v>2.84</v>
       </c>
       <c r="N45" t="n">
-        <v>3.97</v>
+        <v>4.67</v>
       </c>
       <c r="O45" t="n">
         <v>-11.24</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.71</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>459.95</v>
+        <v>436</v>
       </c>
       <c r="I46" t="n">
         <v>438.7111904086973</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>4.14</v>
+        <v>-1.28</v>
       </c>
       <c r="L46" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="M46" t="n">
-        <v>1.11</v>
+        <v>3.03</v>
       </c>
       <c r="N46" t="n">
-        <v>1.18</v>
+        <v>5.88</v>
       </c>
       <c r="O46" t="n">
         <v>4.67</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.09</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45533.55208333334</v>
+        <v>45534.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>430.9</v>
+        <v>433</v>
       </c>
       <c r="I47" t="n">
         <v>432.8976310667236</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>1.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L47" t="n">
         <v>3.88</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>3.61</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>420.7</v>
+        <v>415.9</v>
       </c>
       <c r="I48" t="n">
         <v>419.7809768729911</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.84</v>
+        <v>-3.95</v>
       </c>
       <c r="L48" t="n">
-        <v>3.2</v>
+        <v>4.31</v>
       </c>
       <c r="M48" t="n">
         <v>1</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>4.25</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45544.55208333334</v>
+        <v>45545.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>417.85</v>
+        <v>444</v>
       </c>
       <c r="I49" t="n">
         <v>430.7712633076767</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.47</v>
+        <v>-6.76</v>
       </c>
       <c r="L49" t="n">
-        <v>1.3</v>
+        <v>6.95</v>
       </c>
       <c r="M49" t="n">
-        <v>0.12</v>
+        <v>1.09</v>
       </c>
       <c r="N49" t="n">
-        <v>0.32</v>
+        <v>6.65</v>
       </c>
       <c r="O49" t="n">
         <v>-1</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.67</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>465.9</v>
+        <v>443.2</v>
       </c>
       <c r="I50" t="n">
         <v>457.9402121722109</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K50" t="n">
-        <v>4.93</v>
+        <v>-0.18</v>
       </c>
       <c r="L50" t="n">
         <v>5.29</v>
@@ -3291,7 +3890,7 @@
         <v>2.48</v>
       </c>
       <c r="N50" t="n">
-        <v>2.05</v>
+        <v>5.4</v>
       </c>
       <c r="O50" t="n">
         <v>6.65</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.45</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45631.38541666666</v>
+        <v>45631.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>423.95</v>
+        <v>432.5</v>
       </c>
       <c r="I51" t="n">
         <v>431.8281699928817</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>59</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>4.34</v>
+        <v>2.41</v>
       </c>
       <c r="L51" t="n">
         <v>7.83</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.84</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>422.9</v>
+        <v>420.25</v>
       </c>
       <c r="I52" t="n">
         <v>422.0773435170109</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.22</v>
+        <v>-2.83</v>
       </c>
       <c r="L52" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="M52" t="n">
         <v>0.28</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.31</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>358.1</v>
+        <v>368.75</v>
       </c>
       <c r="I53" t="n">
         <v>364.5334745632852</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>14.79</v>
+        <v>12.25</v>
       </c>
       <c r="L53" t="n">
         <v>0.75</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>357.25</v>
+        <v>350.85</v>
       </c>
       <c r="I54" t="n">
         <v>353.9136250544407</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.12</v>
+        <v>-4.85</v>
       </c>
       <c r="L54" t="n">
-        <v>4.5</v>
+        <v>5.06</v>
       </c>
       <c r="M54" t="n">
         <v>0.55</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.37</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45708.38541666666</v>
+        <v>45708.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>355.4</v>
+        <v>358.5</v>
       </c>
       <c r="I55" t="n">
         <v>357.9931291878256</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.3</v>
+        <v>-2.18</v>
       </c>
       <c r="L55" t="n">
         <v>8.02</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>8.17</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>369.5</v>
+        <v>350.2</v>
       </c>
       <c r="I56" t="n">
         <v>366.1312592763056</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>43</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K56" t="n">
-        <v>3.07</v>
+        <v>-2.32</v>
       </c>
       <c r="L56" t="n">
         <v>7.43</v>
       </c>
       <c r="M56" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N56" t="n">
         <v>4.37</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.61</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>364.8</v>
+        <v>377.8</v>
       </c>
       <c r="I57" t="n">
         <v>376.8428319873545</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.17</v>
+        <v>-7.88</v>
       </c>
       <c r="L57" t="n">
-        <v>5.85</v>
+        <v>8.67</v>
       </c>
       <c r="M57" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="N57" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="O57" t="n">
         <v>-3.44</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.85</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>378.35</v>
+        <v>374.7</v>
       </c>
       <c r="I58" t="n">
         <v>375.2382761225228</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>0.15</v>
+        <v>-0.82</v>
       </c>
       <c r="L58" t="n">
         <v>1.46</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.26</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>371.6</v>
+        <v>388.4</v>
       </c>
       <c r="I59" t="n">
         <v>387.0020710382172</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>0.83</v>
+        <v>-3.66</v>
       </c>
       <c r="L59" t="n">
-        <v>2.38</v>
+        <v>4.48</v>
       </c>
       <c r="M59" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="N59" t="n">
-        <v>1.12</v>
+        <v>5.62</v>
       </c>
       <c r="O59" t="n">
         <v>-3.68</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>7.99</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>400.9</v>
+        <v>395.25</v>
       </c>
       <c r="I60" t="n">
         <v>400.2373361138318</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K60" t="n">
-        <v>3.22</v>
+        <v>1.76</v>
       </c>
       <c r="L60" t="n">
         <v>2.55</v>
       </c>
       <c r="M60" t="n">
-        <v>0.75</v>
+        <v>1.47</v>
       </c>
       <c r="N60" t="n">
         <v>2.69</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>4.48</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>393</v>
+        <v>402.6</v>
       </c>
       <c r="I61" t="n">
         <v>401.8682973121685</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>0.57</v>
+        <v>-1.86</v>
       </c>
       <c r="L61" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="M61" t="n">
-        <v>0.09</v>
+        <v>0.51</v>
       </c>
       <c r="N61" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="O61" t="n">
         <v>-0.64</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.52</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>400.3</v>
+        <v>397.85</v>
       </c>
       <c r="I62" t="n">
         <v>398.3590540898256</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.57</v>
+        <v>-1.18</v>
       </c>
       <c r="L62" t="n">
         <v>1.92</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>3.71</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>380.95</v>
+        <v>387</v>
       </c>
       <c r="I63" t="n">
         <v>384.4866090698655</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K63" t="n">
-        <v>4.25</v>
+        <v>2.73</v>
       </c>
       <c r="L63" t="n">
         <v>1.5</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.23</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>385.6</v>
+        <v>384.2</v>
       </c>
       <c r="I64" t="n">
         <v>385.3207277778794</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.36</v>
+        <v>-0.72</v>
       </c>
       <c r="L64" t="n">
         <v>1.81</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>3.16</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45945.38541666666</v>
+        <v>45945.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>394.5</v>
+        <v>397.1</v>
       </c>
       <c r="I65" t="n">
         <v>396.3416576206081</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.68</v>
+        <v>-3.36</v>
       </c>
       <c r="L65" t="n">
         <v>3.46</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>3.82</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>400.55</v>
+        <v>395.4</v>
       </c>
       <c r="I66" t="n">
         <v>396.5471254552876</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>20</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>0.87</v>
+        <v>-0.43</v>
       </c>
       <c r="L66" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="M66" t="n">
         <v>0.31</v>
       </c>
       <c r="N66" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="O66" t="n">
         <v>1.65</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.48</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>381.6</v>
+        <v>390.55</v>
       </c>
       <c r="I67" t="n">
         <v>383.4074738114846</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K67" t="n">
-        <v>3.49</v>
+        <v>1.23</v>
       </c>
       <c r="L67" t="n">
         <v>1.75</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.05</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>380.55</v>
+        <v>375.7</v>
       </c>
       <c r="I68" t="n">
         <v>380.0204216101508</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.56</v>
+        <v>-3.8</v>
       </c>
       <c r="L68" t="n">
-        <v>2.96</v>
+        <v>4.06</v>
       </c>
       <c r="M68" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="N68" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="O68" t="n">
         <v>2.9</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>4.08</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>355.75</v>
+        <v>364.1</v>
       </c>
       <c r="I69" t="n">
         <v>360.1354098468088</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K69" t="n">
-        <v>5.31</v>
+        <v>3.09</v>
       </c>
       <c r="L69" t="n">
         <v>1.64</v>
@@ -4374,7 +5201,7 @@
         <v>0.47</v>
       </c>
       <c r="N69" t="n">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="O69" t="n">
         <v>-1.79</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,25 +5249,25 @@
         <v>5.54</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>376.6</v>
+        <v>363.9</v>
       </c>
       <c r="I70" t="n">
         <v>364.8920091091729</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K70" t="n">
-        <v>3.43</v>
+        <v>-0.05</v>
       </c>
       <c r="L70" t="n">
         <v>4.31</v>
       </c>
       <c r="M70" t="n">
-        <v>2.17</v>
+        <v>5.47</v>
       </c>
       <c r="N70" t="n">
         <v>3.1</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>5.79</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46091.55208333334</v>
+        <v>46092.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>380.8</v>
+        <v>386.55</v>
       </c>
       <c r="I71" t="n">
         <v>384.9824203234717</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.64</v>
+        <v>-6.22</v>
       </c>
       <c r="L71" t="n">
-        <v>5.87</v>
+        <v>7.86</v>
       </c>
       <c r="M71" t="n">
         <v>0.7</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>5.68</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46104.38541666666</v>
+        <v>46104.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>385.3</v>
+        <v>382.9</v>
       </c>
       <c r="I72" t="n">
         <v>383.0063719671107</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.32</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>1.09</v>
+        <v>3.51</v>
       </c>
       <c r="M72" t="n">
         <v>0.6</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>7.98</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46122.55208333334</v>
+        <v>46125.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>399.5</v>
+        <v>414</v>
       </c>
       <c r="I73" t="n">
         <v>400.540372693583</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>-4.34</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>4.82</v>
+        <v>8.91</v>
       </c>
       <c r="M73" t="n">
         <v>3.21</v>
       </c>
       <c r="N73" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O73" t="n">
         <v>-4.89</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>8.91</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46149.55208333334</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>439.6</v>
+        <v>436.3</v>
       </c>
       <c r="I74" t="n">
         <v>436.718027333856</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K74" t="n">
-        <v>6.18</v>
+        <v>5.39</v>
       </c>
       <c r="L74" t="n">
         <v>5.74</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>4.79</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>421</v>
+        <v>426.4</v>
       </c>
       <c r="I75" t="n">
         <v>424.7378007492262</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K75" t="n">
-        <v>3.51</v>
+        <v>2.27</v>
       </c>
       <c r="L75" t="n">
         <v>0.99</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>5.13</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>409</v>
+        <v>407.6</v>
       </c>
       <c r="I76" t="n">
         <v>407.6773831813548</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.08</v>
+        <v>-4.41</v>
       </c>
       <c r="L76" t="n">
-        <v>4.66</v>
+        <v>5.65</v>
       </c>
       <c r="M76" t="n">
-        <v>0.8</v>
+        <v>1.21</v>
       </c>
       <c r="N76" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="O76" t="n">
         <v>1.64</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>3.7</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46267.38541666666</v>
+        <v>46267.55208333334</v>
       </c>
       <c r="H77" t="n">
-        <v>360.3</v>
+        <v>362.7</v>
       </c>
       <c r="I77" t="n">
         <v>362.3369964935634</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>86</v>
+        <v>86.16666666666667</v>
       </c>
       <c r="K77" t="n">
-        <v>11.6</v>
+        <v>11.02</v>
       </c>
       <c r="L77" t="n">
         <v>0.37</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4</v>
+      </c>
+      <c r="U77" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>4.71</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>358.35</v>
+        <v>351.2</v>
       </c>
       <c r="I78" t="n">
         <v>356.8667070775165</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K78" t="n">
-        <v>-1.2</v>
+        <v>-3.17</v>
       </c>
       <c r="L78" t="n">
-        <v>2.41</v>
+        <v>3.9</v>
       </c>
       <c r="M78" t="n">
-        <v>0.95</v>
+        <v>1.51</v>
       </c>
       <c r="N78" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
         <v>3.66</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>4.62</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46310.55208333334</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>349</v>
+        <v>353.5</v>
       </c>
       <c r="I79" t="n">
         <v>353.0189366362778</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K79" t="n">
-        <v>0.63</v>
+        <v>-0.65</v>
       </c>
       <c r="L79" t="n">
         <v>1.69</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>4.98</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46318.55208333334</v>
+        <v>46321.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>345.9</v>
+        <v>335.8</v>
       </c>
       <c r="I80" t="n">
         <v>339.3677304011792</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.15</v>
+        <v>-5.01</v>
       </c>
       <c r="L80" t="n">
-        <v>3.73</v>
+        <v>5.25</v>
       </c>
       <c r="M80" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="N80" t="n">
-        <v>1.77</v>
+        <v>2.56</v>
       </c>
       <c r="O80" t="n">
         <v>1.15</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,12 @@
       <c r="Q81" t="n">
         <v>4</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7163,7 +8140,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="6">
@@ -7173,7 +8150,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="7">
@@ -7183,7 +8160,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="8">
@@ -7193,7 +8170,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7203,7 +8180,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.5</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="10">
@@ -7213,7 +8190,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.9</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="11">
@@ -7223,7 +8200,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -7233,7 +8210,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -7243,7 +8220,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>81</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="14">
@@ -7253,7 +8230,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.43</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="15">
@@ -7263,7 +8240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.27</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="16">
@@ -7273,7 +8250,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.57</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="17">
@@ -7283,7 +8260,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.73</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="18">
@@ -7293,7 +8270,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.4</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="19">
@@ -7303,7 +8280,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.52</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="20">
@@ -7313,7 +8290,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.94</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="21">
@@ -7323,7 +8300,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.41</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="22">
@@ -7333,7 +8310,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -7343,7 +8320,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -7353,7 +8330,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.98</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
@@ -7363,7 +8340,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -7373,7 +8350,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="27">
@@ -7383,7 +8360,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.51</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="28">
@@ -7393,7 +8370,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
